--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -656,212 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>27300</v>
+      </c>
+      <c r="F8" s="3">
         <v>17800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>24200</v>
       </c>
-      <c r="F8" s="3">
-        <v>27100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>11600</v>
-      </c>
       <c r="H8" s="3">
+        <v>26700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J8" s="3">
         <v>9800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>4400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>6300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F9" s="3">
         <v>10200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>14600</v>
       </c>
-      <c r="F9" s="3">
-        <v>16800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>5500</v>
-      </c>
       <c r="H9" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J9" s="3">
         <v>13300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>5400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F10" s="3">
         <v>7600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>9600</v>
       </c>
-      <c r="F10" s="3">
-        <v>10300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>6100</v>
-      </c>
       <c r="H10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J10" s="3">
         <v>-3500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>5200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,40 +999,46 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>13700</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-7600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-300</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>-400</v>
@@ -1008,43 +1047,49 @@
         <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
       </c>
-      <c r="F15" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1100</v>
-      </c>
       <c r="H15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I15" s="3">
+        <v>900</v>
+      </c>
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1054,8 +1099,14 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1120,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>28500</v>
+      </c>
+      <c r="F17" s="3">
         <v>31600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>26600</v>
       </c>
-      <c r="F17" s="3">
-        <v>21700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>14500</v>
-      </c>
       <c r="H17" s="3">
+        <v>20900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>13600</v>
+      </c>
+      <c r="J17" s="3">
         <v>11300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2900</v>
-      </c>
       <c r="H18" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,96 +1240,110 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-15200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-2300</v>
-      </c>
       <c r="H21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2400</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
       </c>
       <c r="L21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N21" s="3">
         <v>1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1307,96 +1386,114 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-16100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2600</v>
       </c>
-      <c r="F23" s="3">
-        <v>3600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-3400</v>
-      </c>
       <c r="H23" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-2600</v>
+        <v>-700</v>
       </c>
       <c r="E24" s="3">
         <v>-500</v>
       </c>
       <c r="F24" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-1300</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-13500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-13300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
-        <v>3000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H27" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,43 +1686,49 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>200</v>
+      </c>
+      <c r="F29" s="3">
         <v>-2000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J29" s="3">
         <v>-300</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>2800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>1100</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1836,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>800</v>
+      </c>
+      <c r="F32" s="3">
         <v>2400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
-        <v>500</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2135,60 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4500</v>
+        <v>1800</v>
       </c>
       <c r="E41" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="F41" s="3">
         <v>4500</v>
       </c>
       <c r="G41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I41" s="3">
         <v>3300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>13000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>14500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>500</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,207 +2231,237 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F43" s="3">
         <v>8200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>7000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>8900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F44" s="3">
         <v>11600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>10100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>11200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1900</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>8100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F46" s="3">
         <v>25500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>20100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>22100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>18800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>17100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>18300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>10000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>10100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+      <c r="J47" s="3">
+        <v>0</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2260,11 +2469,11 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2272,96 +2481,114 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F48" s="3">
         <v>7900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>8300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>24100</v>
+      </c>
+      <c r="F49" s="3">
         <v>23800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>32400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>34100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>18900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>19100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>13300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>13700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>6900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2681,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F52" s="3">
         <v>6600</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2500</v>
       </c>
       <c r="G52" s="3">
         <v>3100</v>
       </c>
       <c r="H52" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J52" s="3">
         <v>9800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1300</v>
       </c>
       <c r="K52" s="3">
         <v>1300</v>
       </c>
       <c r="L52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N52" s="3">
         <v>1500</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2781,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>65200</v>
+      </c>
+      <c r="F54" s="3">
         <v>63900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>73800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>76600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>49100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>48500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>33200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>35200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>27300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>10000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>9800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,208 +2875,234 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F57" s="3">
         <v>4000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F58" s="3">
         <v>10500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>9200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1800</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F59" s="3">
         <v>5100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>8800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F60" s="3">
         <v>19600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>17700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F61" s="3">
         <v>16200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>19000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>24400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>9700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>8900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2825,63 +3110,75 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>2900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3321,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>37700</v>
+      </c>
+      <c r="F66" s="3">
         <v>35500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>36800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>39700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>22000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>19800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7900</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,52 +3591,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-23200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-7800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-6200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-8900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-6300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-3600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-4200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-6800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-7800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-7900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3791,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>27600</v>
+      </c>
+      <c r="F76" s="3">
         <v>28300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>37000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>36900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>27100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>28700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>28400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>29500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>24800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>21200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4020,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F83" s="3">
         <v>900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>300</v>
+      </c>
+      <c r="R83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>6100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>400</v>
-      </c>
-      <c r="K89" s="3">
-        <v>800</v>
-      </c>
-      <c r="L89" s="3">
-        <v>2800</v>
       </c>
       <c r="M89" s="3">
         <v>800</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="O89" s="3">
+        <v>800</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4390,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-700</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4536,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F94" s="3">
         <v>100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>5900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4610,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4656,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4806,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F100" s="3">
         <v>6600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-10800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>5800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2000</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>11000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4409,48 +4906,60 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F102" s="3">
         <v>3300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>12400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21800</v>
+        <v>14400</v>
       </c>
       <c r="E8" s="3">
+        <v>45100</v>
+      </c>
+      <c r="F8" s="3">
         <v>27300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17800</v>
       </c>
-      <c r="G8" s="3">
-        <v>24200</v>
-      </c>
       <c r="H8" s="3">
-        <v>26700</v>
+        <v>21900</v>
       </c>
       <c r="I8" s="3">
+        <v>34400</v>
+      </c>
+      <c r="J8" s="3">
         <v>11200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>13600</v>
+        <v>11600</v>
       </c>
       <c r="E9" s="3">
+        <v>31300</v>
+      </c>
+      <c r="F9" s="3">
         <v>18600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10200</v>
       </c>
-      <c r="G9" s="3">
-        <v>14600</v>
-      </c>
       <c r="H9" s="3">
-        <v>16700</v>
+        <v>14300</v>
       </c>
       <c r="I9" s="3">
+        <v>21300</v>
+      </c>
+      <c r="J9" s="3">
         <v>5400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8200</v>
+        <v>2800</v>
       </c>
       <c r="E10" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F10" s="3">
         <v>8700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7600</v>
       </c>
-      <c r="G10" s="3">
-        <v>9600</v>
-      </c>
       <c r="H10" s="3">
-        <v>10000</v>
+        <v>7600</v>
       </c>
       <c r="I10" s="3">
+        <v>13100</v>
+      </c>
+      <c r="J10" s="3">
         <v>5800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-3500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,32 +1022,35 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>200</v>
-      </c>
-      <c r="E14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>300</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13700</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-7600</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1038,60 +1058,63 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F15" s="3">
         <v>1500</v>
       </c>
-      <c r="E15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="G15" s="3">
-        <v>1900</v>
-      </c>
       <c r="H15" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="I15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J15" s="3">
         <v>900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>400</v>
       </c>
       <c r="L15" s="3">
         <v>400</v>
       </c>
       <c r="M15" s="3">
+        <v>400</v>
+      </c>
+      <c r="N15" s="3">
         <v>200</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>23800</v>
+        <v>19400</v>
       </c>
       <c r="E17" s="3">
+        <v>48500</v>
+      </c>
+      <c r="F17" s="3">
         <v>28500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31600</v>
       </c>
-      <c r="G17" s="3">
-        <v>26600</v>
-      </c>
       <c r="H17" s="3">
-        <v>20900</v>
+        <v>24000</v>
       </c>
       <c r="I17" s="3">
+        <v>30600</v>
+      </c>
+      <c r="J17" s="3">
         <v>13600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2000</v>
+        <v>-5000</v>
       </c>
       <c r="E18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,108 +1275,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1600</v>
+        <v>-4500</v>
       </c>
       <c r="E21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-500</v>
       </c>
-      <c r="F21" s="3">
-        <v>-15200</v>
-      </c>
       <c r="G21" s="3">
-        <v>-600</v>
+        <v>-14300</v>
       </c>
       <c r="H21" s="3">
-        <v>5400</v>
+        <v>-900</v>
       </c>
       <c r="I21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-400</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
       </c>
       <c r="L21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M21" s="3">
         <v>-2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,108 +1432,117 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3100</v>
+        <v>-5600</v>
       </c>
       <c r="E23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="H23" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-700</v>
       </c>
-      <c r="E24" s="3">
-        <v>-500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H24" s="3">
-        <v>800</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1300</v>
       </c>
-      <c r="O24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2400</v>
+        <v>-4100</v>
       </c>
       <c r="E26" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="H26" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2400</v>
+        <v>-4100</v>
       </c>
       <c r="E27" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1900</v>
-      </c>
       <c r="H27" s="3">
-        <v>3400</v>
+        <v>-1400</v>
       </c>
       <c r="I27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1701,38 +1762,38 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>300</v>
+      </c>
+      <c r="F29" s="3">
         <v>200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-2000</v>
       </c>
-      <c r="G29" s="3">
-        <v>300</v>
-      </c>
       <c r="H29" s="3">
-        <v>-700</v>
+        <v>-300</v>
       </c>
       <c r="I29" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J29" s="3">
         <v>-600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>2800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>1100</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2400</v>
+        <v>-4100</v>
       </c>
       <c r="E33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
-        <v>2700</v>
-      </c>
       <c r="I33" s="3">
-        <v>-2600</v>
+        <v>100</v>
       </c>
       <c r="J33" s="3">
         <v>-2600</v>
       </c>
       <c r="K33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2400</v>
+        <v>-4100</v>
       </c>
       <c r="E35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
-        <v>2700</v>
-      </c>
       <c r="I35" s="3">
-        <v>-2600</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3">
         <v>-2600</v>
       </c>
       <c r="K35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3" t="s">
+      <c r="S41" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,208 +2327,223 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E43" s="3">
         <v>5400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>500</v>
       </c>
-      <c r="R43" s="3" t="s">
+      <c r="S43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E44" s="3">
         <v>14700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1900</v>
       </c>
-      <c r="R44" s="3" t="s">
+      <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
-      </c>
-      <c r="L45" s="3">
-        <v>600</v>
       </c>
       <c r="M45" s="3">
         <v>600</v>
       </c>
       <c r="N45" s="3">
+        <v>600</v>
+      </c>
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
+      <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E46" s="3">
         <v>22600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>20100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3000</v>
       </c>
-      <c r="R46" s="3" t="s">
+      <c r="S46" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2451,20 +2556,20 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>10000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10100</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
+      <c r="K47" s="3">
+        <v>0</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -2475,8 +2580,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2487,108 +2592,117 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>8200</v>
       </c>
       <c r="J48" s="3">
         <v>8200</v>
       </c>
       <c r="K48" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L48" s="3">
         <v>8300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>3200</v>
       </c>
       <c r="N48" s="3">
         <v>3200</v>
       </c>
       <c r="O48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2000</v>
       </c>
-      <c r="R48" s="3" t="s">
+      <c r="S48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E49" s="3">
         <v>23100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>34100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4800</v>
       </c>
-      <c r="R49" s="3" t="s">
+      <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,34 +2804,37 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E52" s="3">
         <v>7200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9800</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1300</v>
       </c>
       <c r="L52" s="3">
         <v>1300</v>
@@ -2723,22 +2843,25 @@
         <v>1300</v>
       </c>
       <c r="N52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O52" s="3">
         <v>1500</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E54" s="3">
         <v>62200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>65200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>63900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>76600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>48500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9800</v>
       </c>
-      <c r="R54" s="3" t="s">
+      <c r="S54" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,235 +3007,248 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>600</v>
       </c>
       <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3" t="s">
+      <c r="R57" s="3">
+        <v>600</v>
+      </c>
+      <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E58" s="3">
         <v>16900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>5400</v>
       </c>
       <c r="J58" s="3">
         <v>5400</v>
       </c>
       <c r="K58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L58" s="3">
         <v>500</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1000</v>
       </c>
       <c r="M58" s="3">
         <v>1000</v>
       </c>
       <c r="N58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1800</v>
       </c>
-      <c r="R58" s="3" t="s">
+      <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E59" s="3">
         <v>4400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4700</v>
       </c>
-      <c r="R59" s="3" t="s">
+      <c r="S59" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E60" s="3">
         <v>24300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7000</v>
       </c>
-      <c r="R60" s="3" t="s">
+      <c r="S60" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E61" s="3">
         <v>11300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8900</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3116,69 +3259,75 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>2900</v>
-      </c>
-      <c r="P61" s="3">
-        <v>600</v>
       </c>
       <c r="Q61" s="3">
         <v>600</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>400</v>
       </c>
       <c r="H62" s="3">
         <v>400</v>
       </c>
       <c r="I62" s="3">
+        <v>400</v>
+      </c>
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>400</v>
-      </c>
-      <c r="M62" s="3">
-        <v>200</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
       </c>
       <c r="O62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>200</v>
       </c>
-      <c r="R62" s="3" t="s">
+      <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E66" s="3">
         <v>36700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>35500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7900</v>
       </c>
-      <c r="R66" s="3" t="s">
+      <c r="S66" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-27000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-24600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-23200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-7800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-6300</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-3600</v>
       </c>
       <c r="L72" s="3">
         <v>-3600</v>
       </c>
       <c r="M72" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="N72" s="3">
         <v>-3700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7900</v>
       </c>
-      <c r="R72" s="3" t="s">
+      <c r="S72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E76" s="3">
         <v>25500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>28300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1900</v>
       </c>
-      <c r="R76" s="3" t="s">
+      <c r="S76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2400</v>
+        <v>-4100</v>
       </c>
       <c r="E81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
-        <v>2700</v>
-      </c>
       <c r="I81" s="3">
-        <v>-2600</v>
+        <v>100</v>
       </c>
       <c r="J81" s="3">
         <v>-2600</v>
       </c>
       <c r="K81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,58 +4220,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1900</v>
       </c>
-      <c r="H83" s="3">
-        <v>1200</v>
-      </c>
       <c r="I83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>300</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
       </c>
       <c r="P83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E89" s="3">
         <v>-2300</v>
       </c>
       <c r="F89" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G89" s="3">
         <v>-3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
-        <v>6100</v>
-      </c>
       <c r="I89" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>800</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4404,46 +4625,49 @@
         <v>-300</v>
       </c>
       <c r="F91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-300</v>
+        <v>500</v>
       </c>
       <c r="E94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
-        <v>100</v>
-      </c>
       <c r="G94" s="3">
-        <v>-5900</v>
+        <v>-1200</v>
       </c>
       <c r="H94" s="3">
-        <v>5900</v>
+        <v>-4600</v>
       </c>
       <c r="I94" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4662,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1700</v>
+        <v>-1200</v>
       </c>
       <c r="E100" s="3">
+        <v>600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2600</v>
       </c>
-      <c r="H100" s="3">
-        <v>-10800</v>
-      </c>
       <c r="I100" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>11000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1400</v>
+        <v>-1300</v>
       </c>
       <c r="E102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3300</v>
       </c>
-      <c r="H102" s="3">
-        <v>1200</v>
-      </c>
       <c r="I102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J102" s="3">
         <v>-3900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -748,19 +748,19 @@
         <v>14400</v>
       </c>
       <c r="E8" s="3">
-        <v>45100</v>
+        <v>17800</v>
       </c>
       <c r="F8" s="3">
         <v>27300</v>
       </c>
-      <c r="G8" s="3">
-        <v>17800</v>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H8" s="3">
         <v>21900</v>
       </c>
       <c r="I8" s="3">
-        <v>34400</v>
+        <v>23200</v>
       </c>
       <c r="J8" s="3">
         <v>11200</v>
@@ -801,19 +801,19 @@
         <v>11600</v>
       </c>
       <c r="E9" s="3">
-        <v>31300</v>
+        <v>12700</v>
       </c>
       <c r="F9" s="3">
         <v>18600</v>
       </c>
-      <c r="G9" s="3">
-        <v>10200</v>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H9" s="3">
         <v>14300</v>
       </c>
       <c r="I9" s="3">
-        <v>21300</v>
+        <v>15800</v>
       </c>
       <c r="J9" s="3">
         <v>5400</v>
@@ -851,22 +851,22 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E10" s="3">
-        <v>13800</v>
+        <v>5100</v>
       </c>
       <c r="F10" s="3">
         <v>8700</v>
       </c>
-      <c r="G10" s="3">
-        <v>7600</v>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H10" s="3">
         <v>7600</v>
       </c>
       <c r="I10" s="3">
-        <v>13100</v>
+        <v>7300</v>
       </c>
       <c r="J10" s="3">
         <v>5800</v>
@@ -1031,19 +1031,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>300</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>13700</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>-7600</v>
@@ -1087,7 +1087,7 @@
         <v>1400</v>
       </c>
       <c r="E15" s="3">
-        <v>2700</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
         <v>1500</v>
@@ -1099,7 +1099,7 @@
         <v>1400</v>
       </c>
       <c r="I15" s="3">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="3">
         <v>900</v>
@@ -1158,19 +1158,19 @@
         <v>19400</v>
       </c>
       <c r="E17" s="3">
-        <v>48500</v>
+        <v>19700</v>
       </c>
       <c r="F17" s="3">
         <v>28500</v>
       </c>
-      <c r="G17" s="3">
-        <v>31600</v>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H17" s="3">
         <v>24000</v>
       </c>
       <c r="I17" s="3">
-        <v>30600</v>
+        <v>24600</v>
       </c>
       <c r="J17" s="3">
         <v>13600</v>
@@ -1208,22 +1208,22 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="E18" s="3">
-        <v>-3400</v>
+        <v>-1900</v>
       </c>
       <c r="F18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-13800</v>
+        <v>-1100</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H18" s="3">
         <v>-2100</v>
       </c>
       <c r="I18" s="3">
-        <v>3800</v>
+        <v>-1400</v>
       </c>
       <c r="J18" s="3">
         <v>-2400</v>
@@ -1281,26 +1281,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-600</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
+        <v>300</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I20" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
@@ -1335,25 +1335,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4500</v>
+        <v>-3600</v>
       </c>
       <c r="E21" s="3">
-        <v>-2300</v>
+        <v>-900</v>
       </c>
       <c r="F21" s="3">
-        <v>-500</v>
+        <v>300</v>
       </c>
       <c r="G21" s="3">
-        <v>-14300</v>
+        <v>900</v>
       </c>
       <c r="H21" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="I21" s="3">
-        <v>3500</v>
+        <v>-300</v>
       </c>
       <c r="J21" s="3">
-        <v>-1900</v>
+        <v>-1500</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
@@ -1388,25 +1388,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1441,22 +1441,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-5600</v>
+        <v>-5700</v>
       </c>
       <c r="E23" s="3">
-        <v>-5300</v>
+        <v>-3300</v>
       </c>
       <c r="F23" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-16100</v>
+        <v>-1600</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H23" s="3">
         <v>-2000</v>
       </c>
       <c r="I23" s="3">
-        <v>1300</v>
+        <v>4100</v>
       </c>
       <c r="J23" s="3">
         <v>-2800</v>
@@ -1497,19 +1497,19 @@
         <v>-1500</v>
       </c>
       <c r="E24" s="3">
-        <v>-1200</v>
+        <v>-700</v>
       </c>
       <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
-        <v>-2600</v>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
         <v>-500</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J24" s="3">
         <v>-700</v>
@@ -1600,22 +1600,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-4100</v>
+        <v>-4200</v>
       </c>
       <c r="E26" s="3">
-        <v>-4100</v>
+        <v>-2600</v>
       </c>
       <c r="F26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-13500</v>
+        <v>-1200</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H26" s="3">
         <v>-1500</v>
       </c>
       <c r="I26" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="J26" s="3">
         <v>-2100</v>
@@ -1656,22 +1656,22 @@
         <v>-4100</v>
       </c>
       <c r="E27" s="3">
-        <v>-4100</v>
+        <v>-2400</v>
       </c>
       <c r="F27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-13300</v>
+        <v>-1400</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H27" s="3">
-        <v>-1400</v>
+        <v>-1600</v>
       </c>
       <c r="I27" s="3">
-        <v>1500</v>
+        <v>2700</v>
       </c>
       <c r="J27" s="3">
-        <v>-2000</v>
+        <v>-2600</v>
       </c>
       <c r="K27" s="3">
         <v>-2300</v>
@@ -1759,22 +1759,22 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F29" s="3">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="G29" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>-300</v>
       </c>
       <c r="I29" s="3">
-        <v>-1400</v>
+        <v>-700</v>
       </c>
       <c r="J29" s="3">
         <v>-600</v>
@@ -1917,26 +1917,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>600</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I32" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
@@ -1974,19 +1974,19 @@
         <v>-4100</v>
       </c>
       <c r="E33" s="3">
-        <v>-3800</v>
+        <v>-2400</v>
       </c>
       <c r="F33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-15400</v>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H33" s="3">
         <v>-1600</v>
       </c>
       <c r="I33" s="3">
-        <v>100</v>
+        <v>2700</v>
       </c>
       <c r="J33" s="3">
         <v>-2600</v>
@@ -2080,19 +2080,19 @@
         <v>-4100</v>
       </c>
       <c r="E35" s="3">
-        <v>-3800</v>
+        <v>-2400</v>
       </c>
       <c r="F35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-15400</v>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H35" s="3">
         <v>-1600</v>
       </c>
       <c r="I35" s="3">
-        <v>100</v>
+        <v>2700</v>
       </c>
       <c r="J35" s="3">
         <v>-2600</v>
@@ -2351,7 +2351,7 @@
         <v>7000</v>
       </c>
       <c r="I43" s="3">
-        <v>8900</v>
+        <v>9300</v>
       </c>
       <c r="J43" s="3">
         <v>1300</v>
@@ -2442,25 +2442,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
-        <v>1000</v>
-      </c>
       <c r="G45" s="3">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="H45" s="3">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="I45" s="3">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="J45" s="3">
-        <v>8100</v>
+        <v>7100</v>
       </c>
       <c r="K45" s="3">
         <v>4900</v>
@@ -2813,25 +2813,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10300</v>
+        <v>2000</v>
       </c>
       <c r="E52" s="3">
-        <v>7200</v>
+        <v>400</v>
       </c>
       <c r="F52" s="3">
-        <v>6400</v>
+        <v>400</v>
       </c>
       <c r="G52" s="3">
-        <v>6600</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="3">
-        <v>3100</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>2500</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>3100</v>
+        <v>400</v>
       </c>
       <c r="K52" s="3">
         <v>9800</v>
@@ -3067,25 +3067,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17500</v>
+        <v>18300</v>
       </c>
       <c r="E58" s="3">
-        <v>16900</v>
+        <v>17700</v>
       </c>
       <c r="F58" s="3">
-        <v>10000</v>
+        <v>10500</v>
       </c>
       <c r="G58" s="3">
-        <v>10500</v>
+        <v>10900</v>
       </c>
       <c r="H58" s="3">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="I58" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="J58" s="3">
-        <v>5400</v>
+        <v>5700</v>
       </c>
       <c r="K58" s="3">
         <v>5400</v>
@@ -3120,25 +3120,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4600</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>4400</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
-        <v>5400</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
-        <v>5100</v>
+        <v>800</v>
       </c>
       <c r="H59" s="3">
-        <v>5900</v>
+        <v>500</v>
       </c>
       <c r="I59" s="3">
-        <v>8800</v>
+        <v>4000</v>
       </c>
       <c r="J59" s="3">
-        <v>4200</v>
+        <v>1600</v>
       </c>
       <c r="K59" s="3">
         <v>3500</v>
@@ -3226,25 +3226,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9200</v>
+        <v>10300</v>
       </c>
       <c r="E61" s="3">
-        <v>11300</v>
+        <v>12400</v>
       </c>
       <c r="F61" s="3">
-        <v>16000</v>
+        <v>17600</v>
       </c>
       <c r="G61" s="3">
-        <v>16200</v>
+        <v>16400</v>
       </c>
       <c r="H61" s="3">
-        <v>19000</v>
+        <v>19400</v>
       </c>
       <c r="I61" s="3">
-        <v>24400</v>
+        <v>24800</v>
       </c>
       <c r="J61" s="3">
-        <v>9700</v>
+        <v>10300</v>
       </c>
       <c r="K61" s="3">
         <v>8900</v>
@@ -3278,26 +3278,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1100</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>600</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>700</v>
@@ -3500,16 +3500,16 @@
         <v>37700</v>
       </c>
       <c r="G66" s="3">
-        <v>35500</v>
+        <v>36000</v>
       </c>
       <c r="H66" s="3">
-        <v>36800</v>
+        <v>37100</v>
       </c>
       <c r="I66" s="3">
-        <v>39700</v>
+        <v>39900</v>
       </c>
       <c r="J66" s="3">
-        <v>22000</v>
+        <v>22100</v>
       </c>
       <c r="K66" s="3">
         <v>19800</v>
@@ -4156,19 +4156,19 @@
         <v>-4100</v>
       </c>
       <c r="E81" s="3">
-        <v>-3800</v>
+        <v>-2400</v>
       </c>
       <c r="F81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-15400</v>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H81" s="3">
         <v>-1600</v>
       </c>
       <c r="I81" s="3">
-        <v>100</v>
+        <v>2700</v>
       </c>
       <c r="J81" s="3">
         <v>-2600</v>
@@ -4227,25 +4227,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>1900</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>2300</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>1300</v>
@@ -4548,19 +4548,19 @@
         <v>-700</v>
       </c>
       <c r="E89" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-3300</v>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H89" s="3">
-        <v>-100</v>
+        <v>-1400</v>
       </c>
       <c r="I89" s="3">
-        <v>3600</v>
+        <v>6100</v>
       </c>
       <c r="J89" s="3">
         <v>-2500</v>
@@ -4622,13 +4622,13 @@
         <v>-300</v>
       </c>
       <c r="E91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-700</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -4781,19 +4781,19 @@
         <v>500</v>
       </c>
       <c r="E94" s="3">
-        <v>-900</v>
+        <v>-300</v>
       </c>
       <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1200</v>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3">
         <v>-4600</v>
       </c>
       <c r="I94" s="3">
-        <v>3200</v>
+        <v>5900</v>
       </c>
       <c r="J94" s="3">
         <v>-2600</v>
@@ -4851,26 +4851,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5067,19 +5067,19 @@
         <v>-1200</v>
       </c>
       <c r="E100" s="3">
-        <v>600</v>
+        <v>1700</v>
       </c>
       <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
-        <v>6600</v>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H100" s="3">
         <v>2600</v>
       </c>
       <c r="I100" s="3">
-        <v>-9500</v>
+        <v>-10800</v>
       </c>
       <c r="J100" s="3">
         <v>1300</v>
@@ -5116,26 +5116,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5173,19 +5173,19 @@
         <v>-1300</v>
       </c>
       <c r="E102" s="3">
-        <v>-2600</v>
+        <v>1400</v>
       </c>
       <c r="F102" s="3">
         <v>-4100</v>
       </c>
       <c r="G102" s="3">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-3300</v>
       </c>
       <c r="I102" s="3">
-        <v>-2600</v>
+        <v>1200</v>
       </c>
       <c r="J102" s="3">
         <v>-3900</v>

--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -656,250 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3">
         <v>14400</v>
       </c>
-      <c r="E8" s="3">
-        <v>17800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>27300</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>21900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>23200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>11200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>9800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>4400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>5000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>3900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>10600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="S8" s="3">
         <v>6300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="T8" s="3">
         <v>4200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="U8" s="3">
         <v>2900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="G9" s="3">
         <v>11600</v>
       </c>
-      <c r="E9" s="3">
-        <v>12700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>18600</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="K9" s="3">
         <v>14300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>15800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>5400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>13300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>5400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>3000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>2200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>1600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2900</v>
       </c>
-      <c r="E10" s="3">
-        <v>5100</v>
-      </c>
       <c r="F10" s="3">
-        <v>8700</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
+        <v>-3900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2900</v>
       </c>
       <c r="H10" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>300</v>
+      </c>
+      <c r="K10" s="3">
         <v>7600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>7300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>5800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <v>-3500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>3300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>4300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>2600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>5200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="S10" s="3">
         <v>3300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="T10" s="3">
         <v>2000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="U10" s="3">
         <v>1300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="V10" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +957,11 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +1013,17 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,114 +1075,141 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>-7600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="R14" s="3">
         <v>-400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>-400</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G15" s="3">
         <v>1400</v>
       </c>
-      <c r="E15" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K15" s="3">
         <v>1400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="M15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="N15" s="3">
         <v>700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="O15" s="3">
         <v>400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="P15" s="3">
         <v>400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="Q15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1226,135 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F17" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="G17" s="3">
         <v>19400</v>
       </c>
-      <c r="E17" s="3">
-        <v>19700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>28500</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H17" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I17" s="3">
+        <v>9700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="K17" s="3">
         <v>24000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>24600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>13600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>11300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>6000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>7500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>4400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>8800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="S17" s="3">
         <v>5300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>4000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>3700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="G18" s="3">
         <v>-4900</v>
       </c>
-      <c r="E18" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-2400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="S18" s="3">
         <v>1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="U18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="V18" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,147 +1374,168 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="G21" s="3">
         <v>-3600</v>
       </c>
-      <c r="E21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F21" s="3">
-        <v>300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>900</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="M21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-2400</v>
       </c>
       <c r="N21" s="3">
         <v>-400</v>
       </c>
       <c r="O21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R21" s="3">
         <v>1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="S21" s="3">
         <v>1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="T21" s="3">
         <v>300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>-500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="V21" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
+        <v>500</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>900</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
+      <c r="H22" s="3">
+        <v>1000</v>
       </c>
       <c r="I22" s="3">
+        <v>800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>1900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1435,114 +1554,141 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="E23" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L23" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
         <v>100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="U23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="H24" s="3">
         <v>-700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>-1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="R24" s="3">
         <v>-1300</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1740,141 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="G26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="L26" s="3">
         <v>3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="U26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>-1400</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="S27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,61 +1926,79 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G29" s="3">
         <v>100</v>
       </c>
-      <c r="E29" s="3">
-        <v>200</v>
-      </c>
-      <c r="F29" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
-        <v>-300</v>
+        <v>500</v>
       </c>
       <c r="I29" s="3">
-        <v>-700</v>
+        <v>100</v>
       </c>
       <c r="J29" s="3">
-        <v>-600</v>
+        <v>300</v>
       </c>
       <c r="K29" s="3">
         <v>-300</v>
       </c>
       <c r="L29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M29" s="3">
+        <v>-600</v>
+      </c>
+      <c r="N29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O29" s="3">
         <v>100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="P29" s="3">
         <v>2800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="Q29" s="3">
         <v>1100</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +2050,17 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +2112,141 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
+        <v>300</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>-1400</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="S33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2298,146 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>-1400</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="S35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2457,11 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2481,73 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E41" s="3">
         <v>1800</v>
       </c>
       <c r="F41" s="3">
+        <v>700</v>
+      </c>
+      <c r="G41" s="3">
+        <v>500</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>4500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
-      </c>
-      <c r="I41" s="3">
-        <v>4500</v>
-      </c>
-      <c r="J41" s="3">
-        <v>3300</v>
-      </c>
-      <c r="K41" s="3">
-        <v>7100</v>
       </c>
       <c r="L41" s="3">
         <v>4500</v>
       </c>
       <c r="M41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="O41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="P41" s="3">
         <v>6600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>13000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>14500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>2100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,220 +2599,265 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G43" s="3">
         <v>4900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>5400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>9800</v>
       </c>
-      <c r="G43" s="3">
-        <v>8200</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K43" s="3">
         <v>7000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>9300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>1500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>1200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="S43" s="3">
         <v>600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="U43" s="3">
         <v>500</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G44" s="3">
         <v>8800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>14700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>13800</v>
       </c>
-      <c r="G44" s="3">
-        <v>11600</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K44" s="3">
         <v>10100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>6800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>6100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>11200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>3600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>3700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>3100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>2100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>2300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>1800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>1900</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2400</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>300</v>
       </c>
       <c r="F45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
-        <v>900</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
+        <v>18400</v>
+      </c>
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>7100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>4900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>11400</v>
+      </c>
+      <c r="G46" s="3">
         <v>16800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>22600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>24900</v>
       </c>
-      <c r="G46" s="3">
-        <v>25500</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
+        <v>30000</v>
+      </c>
+      <c r="K46" s="3">
         <v>20100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>22100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>18800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>17100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>10300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>12100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>17800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>18300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="3">
         <v>5700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="T46" s="3">
         <v>3500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="U46" s="3">
         <v>3000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2559,150 +2873,177 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>10000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>10100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
+      <c r="N47" s="3">
+        <v>0</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>9300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>9800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>7900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>8300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>7800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>8200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>8200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>8300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>8100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>3200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>3200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>1900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="U48" s="3">
         <v>2000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G49" s="3">
         <v>20300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>23100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>24100</v>
       </c>
-      <c r="G49" s="3">
-        <v>23800</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K49" s="3">
         <v>32400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>34100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>18900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>19100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>13300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>13700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>6900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="R49" s="3">
         <v>4300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="S49" s="3">
         <v>4400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="T49" s="3">
         <v>4600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="U49" s="3">
         <v>4800</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +3095,17 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,61 +3157,79 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>300</v>
+      </c>
+      <c r="G52" s="3">
         <v>2000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>9800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>1300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>1300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>1300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="R52" s="3">
         <v>1500</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3281,79 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F54" s="3">
+        <v>23500</v>
+      </c>
+      <c r="G54" s="3">
         <v>56500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>62200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>65200</v>
       </c>
-      <c r="G54" s="3">
-        <v>63900</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
+        <v>63800</v>
+      </c>
+      <c r="K54" s="3">
         <v>73800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>76600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>49100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>48500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>33200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>35200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>29200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="R54" s="3">
         <v>27300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="S54" s="3">
         <v>11900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="T54" s="3">
         <v>10000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="U54" s="3">
         <v>9800</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3373,11 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,273 +3397,321 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>600</v>
+      </c>
+      <c r="F57" s="3">
+        <v>500</v>
+      </c>
+      <c r="G57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>4600</v>
       </c>
-      <c r="G57" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K57" s="3">
         <v>2600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>4200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="S57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G58" s="3">
         <v>18300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>17700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>10500</v>
       </c>
-      <c r="G58" s="3">
-        <v>10900</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
+        <v>12800</v>
+      </c>
+      <c r="K58" s="3">
         <v>9400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>2300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>5700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>5400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="R58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="S58" s="3">
         <v>1200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="T58" s="3">
         <v>2500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="U58" s="3">
         <v>1800</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>600</v>
+      </c>
+      <c r="F59" s="3">
+        <v>600</v>
+      </c>
+      <c r="G59" s="3">
         <v>400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
-        <v>800</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>3500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>2600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="R59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>3600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="T59" s="3">
         <v>4000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="U59" s="3">
         <v>4700</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F60" s="3">
+        <v>12700</v>
+      </c>
+      <c r="G60" s="3">
         <v>24200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>24300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>20000</v>
       </c>
-      <c r="G60" s="3">
-        <v>19600</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
+        <v>22400</v>
+      </c>
+      <c r="K60" s="3">
         <v>17700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>15100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>11700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>10100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>4400</v>
-      </c>
-      <c r="M60" s="3">
-        <v>5300</v>
-      </c>
-      <c r="N60" s="3">
-        <v>4200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>5800</v>
       </c>
       <c r="P60" s="3">
         <v>5300</v>
       </c>
       <c r="Q60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R60" s="3">
+        <v>5800</v>
+      </c>
+      <c r="S60" s="3">
+        <v>5300</v>
+      </c>
+      <c r="T60" s="3">
         <v>7100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="U60" s="3">
         <v>7000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G61" s="3">
         <v>10300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>12400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>17600</v>
       </c>
-      <c r="G61" s="3">
-        <v>16400</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
+        <v>13600</v>
+      </c>
+      <c r="K61" s="3">
         <v>19400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>24800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>10300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>8900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>2900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="T61" s="3">
         <v>600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="U61" s="3">
         <v>600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3299,35 +3736,44 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>200</v>
-      </c>
-      <c r="O62" s="3">
-        <v>200</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
       </c>
       <c r="R62" s="3">
         <v>200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>200</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3825,17 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3887,17 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3949,79 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>17000</v>
+      </c>
+      <c r="G66" s="3">
         <v>34500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>36700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>37700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>36000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>37100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>39900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>22100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>19800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>4700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>5700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>4400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>6000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>8200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>7700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>7900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +4041,11 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +4097,17 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +4159,17 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +4221,17 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +4283,79 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-49800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="G72" s="3">
         <v>-31100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>-27000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>-24600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>-23200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>-7800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-6200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-8900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-6300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>-3600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>-3600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>-3700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>-4200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-7800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>-7900</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4407,17 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4469,17 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4531,79 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G76" s="3">
         <v>22100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>25500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>27600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>28300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>37000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>36900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>27100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>28700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>28400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>29500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>24800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>21200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>3700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>2300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>1900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4655,146 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>-1400</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="S81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4814,11 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4230,16 +4826,16 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -4248,34 +4844,43 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
         <v>1300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>900</v>
-      </c>
-      <c r="N83" s="3">
-        <v>400</v>
       </c>
       <c r="O83" s="3">
         <v>300</v>
       </c>
       <c r="P83" s="3">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="Q83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
       </c>
       <c r="S83" s="3">
+        <v>300</v>
+      </c>
+      <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
+        <v>300</v>
+      </c>
+      <c r="V83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4932,17 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4994,17 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +5056,17 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +5118,17 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +5180,79 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H89" s="3">
+        <v>200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>2800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>800</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="V89" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +5272,73 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-4100</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +5390,17 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +5452,79 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G94" s="3">
         <v>500</v>
       </c>
-      <c r="E94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-2600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="V94" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5544,11 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4872,14 +5573,14 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4899,8 +5600,17 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5662,17 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5724,17 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,61 +5786,79 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>200</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1200</v>
       </c>
-      <c r="E100" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H100" s="3">
+        <v>900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J100" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K100" s="3">
         <v>2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-10800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>5800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>11000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="S100" s="3">
         <v>300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5137,14 +5883,14 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5164,57 +5910,75 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>200</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>12400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="S102" s="3">
         <v>900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="T102" s="3">
         <v>700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="V102" s="3">
         <v>-2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4400</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
         <v>14400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8300</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>21900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>-29700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>-20100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E10" s="3">
         <v>3000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-3900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-3500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,43 +1101,46 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-7600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1129,25 +1149,28 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-400</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-400</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,47 +1178,47 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
+        <v>200</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>700</v>
-      </c>
-      <c r="O15" s="3">
-        <v>400</v>
       </c>
       <c r="P15" s="3">
         <v>400</v>
       </c>
       <c r="Q15" s="3">
+        <v>400</v>
+      </c>
+      <c r="R15" s="3">
         <v>200</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>-20300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-13500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,132 +1410,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-400</v>
       </c>
       <c r="O21" s="3">
         <v>-400</v>
       </c>
       <c r="P21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1510,35 +1550,35 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2300</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>1900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1563,70 +1603,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1636,50 +1682,50 @@
       <c r="E24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3">
         <v>2300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1687,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1947,46 +2008,46 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>1100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>2800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1100</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2700</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-2600</v>
       </c>
       <c r="N33" s="3">
         <v>-2600</v>
       </c>
       <c r="O33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="P33" s="3">
         <v>-100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2700</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-2600</v>
       </c>
       <c r="N35" s="3">
         <v>-2600</v>
       </c>
       <c r="O35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="P35" s="3">
         <v>-100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
         <v>400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,256 +2698,271 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>500</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1900</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
       </c>
       <c r="Q45" s="3">
         <v>600</v>
       </c>
       <c r="R45" s="3">
+        <v>600</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>30000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>20100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2882,20 +2987,20 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>10000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
@@ -2906,8 +3011,8 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -2918,75 +3023,81 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7800</v>
-      </c>
-      <c r="M48" s="3">
-        <v>8200</v>
       </c>
       <c r="N48" s="3">
         <v>8200</v>
       </c>
       <c r="O48" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P48" s="3">
         <v>8300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>3200</v>
       </c>
       <c r="R48" s="3">
         <v>3200</v>
       </c>
       <c r="S48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T48" s="3">
         <v>1800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="3">
         <v>1100</v>
@@ -2995,55 +3106,58 @@
         <v>1100</v>
       </c>
       <c r="G49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H49" s="3">
         <v>20300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>32400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>34100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4800</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3178,34 +3298,34 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
+        <v>200</v>
+      </c>
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>400</v>
       </c>
       <c r="I52" s="3">
         <v>400</v>
       </c>
       <c r="J52" s="3">
+        <v>400</v>
+      </c>
+      <c r="K52" s="3">
         <v>10500</v>
-      </c>
-      <c r="K52" s="3">
-        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9800</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1300</v>
       </c>
       <c r="P52" s="3">
         <v>1300</v>
@@ -3214,22 +3334,25 @@
         <v>1300</v>
       </c>
       <c r="R52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S52" s="3">
         <v>1500</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E54" s="3">
         <v>17500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>56500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>62200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>65200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>49100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>48500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>35200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9800</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,137 +3530,144 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
-      </c>
-      <c r="T57" s="3">
-        <v>600</v>
       </c>
       <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>600</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>1000</v>
       </c>
       <c r="Q58" s="3">
         <v>1000</v>
       </c>
       <c r="R58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S58" s="3">
         <v>400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1800</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
         <v>600</v>
@@ -3539,156 +3676,162 @@
         <v>600</v>
       </c>
       <c r="G59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H59" s="3">
         <v>400</v>
       </c>
       <c r="I59" s="3">
+        <v>400</v>
+      </c>
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4700</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E60" s="3">
         <v>10600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>24200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>24300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8900</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3699,19 +3842,22 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>2900</v>
-      </c>
-      <c r="T61" s="3">
-        <v>600</v>
       </c>
       <c r="U61" s="3">
         <v>600</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3745,35 +3891,38 @@
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>400</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>200</v>
       </c>
       <c r="R62" s="3">
         <v>200</v>
       </c>
       <c r="S62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E66" s="3">
         <v>13800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>34500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>37700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>36000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-49800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-48500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-46900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-31100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-27000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-24600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-23200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-6200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6300</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-3600</v>
       </c>
       <c r="P72" s="3">
         <v>-3600</v>
       </c>
       <c r="Q72" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="R72" s="3">
         <v>-3700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7900</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E76" s="3">
         <v>3800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>27600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>28300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>37000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>36900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>29500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>21200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2700</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-2600</v>
       </c>
       <c r="N81" s="3">
         <v>-2600</v>
       </c>
       <c r="O81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="P81" s="3">
         <v>-100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,22 +5015,23 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -4841,46 +5040,49 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
       </c>
       <c r="T83" s="3">
+        <v>300</v>
+      </c>
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>800</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5284,61 +5505,64 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>5800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5582,8 +5816,8 @@
       <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5892,8 +6141,8 @@
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -772,7 +772,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="3">
-        <v>14400</v>
+        <v>5200</v>
       </c>
       <c r="I8" s="3">
         <v>7500</v>
@@ -837,7 +837,7 @@
         <v>-29700</v>
       </c>
       <c r="H9" s="3">
-        <v>11600</v>
+        <v>4000</v>
       </c>
       <c r="I9" s="3">
         <v>2900</v>
@@ -902,7 +902,7 @@
         <v>-3900</v>
       </c>
       <c r="H10" s="3">
-        <v>2900</v>
+        <v>1300</v>
       </c>
       <c r="I10" s="3">
         <v>4600</v>
@@ -1187,7 +1187,7 @@
         <v>7500</v>
       </c>
       <c r="H15" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="3">
         <v>1000</v>
@@ -1274,7 +1274,7 @@
         <v>-20300</v>
       </c>
       <c r="H17" s="3">
-        <v>19400</v>
+        <v>10300</v>
       </c>
       <c r="I17" s="3">
         <v>9800</v>
@@ -1339,7 +1339,7 @@
         <v>-13300</v>
       </c>
       <c r="H18" s="3">
-        <v>-4900</v>
+        <v>-5000</v>
       </c>
       <c r="I18" s="3">
         <v>-2300</v>
@@ -1428,8 +1428,8 @@
       <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>300</v>
@@ -1494,7 +1494,7 @@
         <v>-5600</v>
       </c>
       <c r="H21" s="3">
-        <v>-3600</v>
+        <v>-4100</v>
       </c>
       <c r="I21" s="3">
         <v>-1600</v>
@@ -1624,7 +1624,7 @@
         <v>-14500</v>
       </c>
       <c r="H23" s="3">
-        <v>-5700</v>
+        <v>-5900</v>
       </c>
       <c r="I23" s="3">
         <v>-3700</v>
@@ -1819,7 +1819,7 @@
         <v>-16900</v>
       </c>
       <c r="H26" s="3">
-        <v>-4200</v>
+        <v>-4400</v>
       </c>
       <c r="I26" s="3">
         <v>-3000</v>
@@ -2014,7 +2014,7 @@
         <v>1100</v>
       </c>
       <c r="H29" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I29" s="3">
         <v>500</v>
@@ -2208,8 +2208,8 @@
       <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>-300</v>
@@ -2836,8 +2836,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
@@ -5022,7 +5022,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -5424,7 +5424,7 @@
         <v>2900</v>
       </c>
       <c r="H89" s="3">
-        <v>-700</v>
+        <v>800</v>
       </c>
       <c r="I89" s="3">
         <v>200</v>
@@ -5514,7 +5514,7 @@
         <v>-200</v>
       </c>
       <c r="H91" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="I91" s="3">
         <v>-200</v>
@@ -5709,7 +5709,7 @@
         <v>-3000</v>
       </c>
       <c r="H94" s="3">
-        <v>500</v>
+        <v>-200</v>
       </c>
       <c r="I94" s="3">
         <v>-1000</v>
@@ -6059,7 +6059,7 @@
         <v>200</v>
       </c>
       <c r="H100" s="3">
-        <v>-1200</v>
+        <v>-900</v>
       </c>
       <c r="I100" s="3">
         <v>900</v>
@@ -6189,7 +6189,7 @@
         <v>200</v>
       </c>
       <c r="H102" s="3">
-        <v>-1300</v>
+        <v>-300</v>
       </c>
       <c r="I102" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -656,327 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E8" s="3">
         <v>9200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8300</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>21900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-20100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>14300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E10" s="3">
         <v>8300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-3500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,52 +1160,55 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>9000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-7600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1198,25 +1217,28 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-400</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>-400</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1224,56 +1246,56 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>1000</v>
       </c>
       <c r="L15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M15" s="3">
         <v>900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>700</v>
-      </c>
-      <c r="R15" s="3">
-        <v>400</v>
       </c>
       <c r="S15" s="3">
         <v>400</v>
       </c>
       <c r="T15" s="3">
+        <v>400</v>
+      </c>
+      <c r="U15" s="3">
         <v>200</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E17" s="3">
         <v>-59900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-13500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-173900</v>
+      </c>
+      <c r="E18" s="3">
         <v>69200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-6500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,195 +1511,202 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-173700</v>
+      </c>
+      <c r="E21" s="3">
         <v>69600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-400</v>
       </c>
       <c r="R21" s="3">
         <v>-400</v>
       </c>
       <c r="S21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E22" s="3">
         <v>2700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
       </c>
       <c r="G22" s="3">
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>1900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1692,79 +1731,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-178900</v>
+      </c>
+      <c r="E23" s="3">
         <v>66700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1783,50 +1828,50 @@
       <c r="H24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1300</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -1834,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-178900</v>
+      </c>
+      <c r="E26" s="3">
         <v>66700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-178900</v>
+      </c>
+      <c r="E27" s="3">
         <v>66700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2139,46 +2199,46 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>2800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1100</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-178900</v>
+      </c>
+      <c r="E33" s="3">
         <v>66700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2700</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-2600</v>
       </c>
       <c r="Q33" s="3">
         <v>-2600</v>
       </c>
       <c r="R33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-178900</v>
+      </c>
+      <c r="E35" s="3">
         <v>66700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2700</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-2600</v>
       </c>
       <c r="Q35" s="3">
         <v>-2600</v>
       </c>
       <c r="R35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="3">
         <v>2200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>500</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,301 +2976,316 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>500</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>8800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>11200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1900</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>165800</v>
+      </c>
+      <c r="E45" s="3">
         <v>214200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>200</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
-      </c>
-      <c r="S45" s="3">
-        <v>600</v>
       </c>
       <c r="T45" s="3">
         <v>600</v>
       </c>
       <c r="U45" s="3">
+        <v>600</v>
+      </c>
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E46" s="3">
         <v>220300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>56800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>10300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>800</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3206,20 +3310,20 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>10000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
@@ -3230,8 +3334,8 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3242,84 +3346,90 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7800</v>
-      </c>
-      <c r="P48" s="3">
-        <v>8200</v>
       </c>
       <c r="Q48" s="3">
         <v>8200</v>
       </c>
       <c r="R48" s="3">
+        <v>8200</v>
+      </c>
+      <c r="S48" s="3">
         <v>8300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8100</v>
-      </c>
-      <c r="T48" s="3">
-        <v>3200</v>
       </c>
       <c r="U48" s="3">
         <v>3200</v>
       </c>
       <c r="V48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="W48" s="3">
         <v>1800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E49" s="3">
         <v>1000</v>
@@ -3328,7 +3438,7 @@
         <v>1000</v>
       </c>
       <c r="G49" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="H49" s="3">
         <v>1100</v>
@@ -3337,55 +3447,58 @@
         <v>1100</v>
       </c>
       <c r="J49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K49" s="3">
         <v>20300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>32400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>34100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4800</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,19 +3642,22 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E52" s="3">
         <v>188200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>56300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
@@ -3546,35 +3665,35 @@
       <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="I52" s="3">
+        <v>200</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>2000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
       </c>
       <c r="M52" s="3">
+        <v>400</v>
+      </c>
+      <c r="N52" s="3">
         <v>10500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>100</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9800</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1300</v>
       </c>
       <c r="S52" s="3">
         <v>1300</v>
@@ -3583,22 +3702,25 @@
         <v>1300</v>
       </c>
       <c r="U52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V52" s="3">
         <v>1500</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E54" s="3">
         <v>419700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>123800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>56500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>62200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>63800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>73800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>76600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>49100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>48500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>33200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>29200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,164 +3922,171 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
-      </c>
-      <c r="W57" s="3">
-        <v>600</v>
       </c>
       <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E58" s="3">
         <v>56500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>26600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>500</v>
-      </c>
-      <c r="S58" s="3">
-        <v>1000</v>
       </c>
       <c r="T58" s="3">
         <v>1000</v>
       </c>
       <c r="U58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V58" s="3">
         <v>400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1800</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>300</v>
       </c>
       <c r="G59" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H59" s="3">
         <v>600</v>
@@ -3959,174 +4095,180 @@
         <v>600</v>
       </c>
       <c r="J59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="K59" s="3">
         <v>400</v>
       </c>
       <c r="L59" s="3">
+        <v>400</v>
+      </c>
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E60" s="3">
         <v>64600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>22400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>144600</v>
+      </c>
+      <c r="E61" s="3">
         <v>144300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4137,19 +4279,22 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>2900</v>
-      </c>
-      <c r="W61" s="3">
-        <v>600</v>
       </c>
       <c r="X61" s="3">
         <v>600</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4192,35 +4337,38 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>400</v>
-      </c>
-      <c r="T62" s="3">
-        <v>200</v>
       </c>
       <c r="U62" s="3">
         <v>200</v>
       </c>
       <c r="V62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
       <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>222400</v>
+      </c>
+      <c r="E66" s="3">
         <v>208900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>33700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>34500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>22100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>19800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7900</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-172700</v>
+      </c>
+      <c r="E72" s="3">
         <v>6200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-60500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-53600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-49800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-48500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-46900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-31100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6300</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-3600</v>
       </c>
       <c r="S72" s="3">
         <v>-3600</v>
       </c>
       <c r="T72" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="U72" s="3">
         <v>-3700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E76" s="3">
         <v>210800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>90100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>27600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>36900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>27100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>28700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>29500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-178900</v>
+      </c>
+      <c r="E81" s="3">
         <v>66700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2700</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-2600</v>
       </c>
       <c r="Q81" s="3">
         <v>-2600</v>
       </c>
       <c r="R81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5423,22 +5621,22 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -5447,46 +5645,49 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>400</v>
-      </c>
-      <c r="U83" s="3">
-        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>300</v>
       </c>
       <c r="W83" s="3">
+        <v>300</v>
+      </c>
+      <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-9800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>800</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6157,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5947,70 +6167,73 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-105100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6293,8 +6526,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +6775,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E100" s="3">
         <v>39400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>112100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2000</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>11000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6648,8 +6896,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6675,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-4000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPXI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>UPXI</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E8" s="3">
         <v>8100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8300</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>21900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>23200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7400</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>-20100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E10" s="3">
         <v>6700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-3500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,55 +1180,58 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>9000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1220,85 +1240,88 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-400</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-400</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
       </c>
       <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1000</v>
       </c>
       <c r="L15" s="3">
         <v>1000</v>
       </c>
       <c r="M15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N15" s="3">
         <v>900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>700</v>
-      </c>
-      <c r="S15" s="3">
-        <v>400</v>
       </c>
       <c r="T15" s="3">
         <v>400</v>
       </c>
       <c r="U15" s="3">
+        <v>400</v>
+      </c>
+      <c r="V15" s="3">
         <v>200</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E17" s="3">
         <v>182000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-59900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-13500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-106800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-173900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>69200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,204 +1545,211 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
+      <c r="H20" s="3">
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-105600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-173700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>69600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-400</v>
       </c>
       <c r="S21" s="3">
         <v>-400</v>
       </c>
       <c r="T21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="U21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E22" s="3">
         <v>3600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>200</v>
       </c>
       <c r="I22" s="3">
+        <v>200</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2300</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1734,82 +1774,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-178900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>66700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1831,50 +1877,50 @@
       <c r="I24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1300</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -1882,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-178900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>66700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-178900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>66700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2202,46 +2263,46 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>2800</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1100</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
+      <c r="H32" s="3">
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-178900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>66700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-2600</v>
       </c>
       <c r="R33" s="3">
         <v>-2600</v>
       </c>
       <c r="S33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-178900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>66700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-2600</v>
       </c>
       <c r="R35" s="3">
         <v>-2600</v>
       </c>
       <c r="S35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,316 +3069,331 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>500</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>200</v>
+      </c>
+      <c r="E44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>11200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1900</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E45" s="3">
         <v>165800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>214200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
       </c>
       <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
-      </c>
-      <c r="T45" s="3">
-        <v>600</v>
       </c>
       <c r="U45" s="3">
         <v>600</v>
       </c>
       <c r="V45" s="3">
+        <v>600</v>
+      </c>
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>121800</v>
+      </c>
+      <c r="E46" s="3">
         <v>171300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>220300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>56800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>10300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>800</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3313,20 +3418,20 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>10000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
@@ -3337,8 +3442,8 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3349,82 +3454,88 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7800</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>8200</v>
       </c>
       <c r="R48" s="3">
         <v>8200</v>
       </c>
       <c r="S48" s="3">
+        <v>8200</v>
+      </c>
+      <c r="T48" s="3">
         <v>8300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>3200</v>
       </c>
       <c r="V48" s="3">
         <v>3200</v>
       </c>
       <c r="W48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X48" s="3">
         <v>1800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3432,7 +3543,7 @@
         <v>1500</v>
       </c>
       <c r="E49" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F49" s="3">
         <v>1000</v>
@@ -3441,7 +3552,7 @@
         <v>1000</v>
       </c>
       <c r="H49" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I49" s="3">
         <v>1100</v>
@@ -3450,55 +3561,58 @@
         <v>1100</v>
       </c>
       <c r="K49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L49" s="3">
         <v>20300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>24100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>32400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>34100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4800</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,22 +3762,25 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E52" s="3">
         <v>91200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>188200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>56300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
@@ -3668,35 +3788,35 @@
       <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="J52" s="3">
+        <v>200</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>2000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>400</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
       </c>
       <c r="N52" s="3">
+        <v>400</v>
+      </c>
+      <c r="O52" s="3">
         <v>10500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>100</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
       <c r="Q52" s="3">
+        <v>100</v>
+      </c>
+      <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9800</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1300</v>
       </c>
       <c r="T52" s="3">
         <v>1300</v>
@@ -3705,22 +3825,25 @@
         <v>1300</v>
       </c>
       <c r="V52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W52" s="3">
         <v>1500</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E54" s="3">
         <v>271100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>419700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>123800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>62200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>65200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>63800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>73800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>76600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>49100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>48500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>29200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>27300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9800</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,173 +4053,180 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
-      </c>
-      <c r="X57" s="3">
-        <v>600</v>
       </c>
       <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E58" s="3">
         <v>68900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>56500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>26600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>500</v>
-      </c>
-      <c r="T58" s="3">
-        <v>1000</v>
       </c>
       <c r="U58" s="3">
         <v>1000</v>
       </c>
       <c r="V58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W58" s="3">
         <v>400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1800</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>300</v>
       </c>
       <c r="G59" s="3">
         <v>300</v>
       </c>
       <c r="H59" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I59" s="3">
         <v>600</v>
@@ -4098,180 +4235,186 @@
         <v>600</v>
       </c>
       <c r="K59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="L59" s="3">
         <v>400</v>
       </c>
       <c r="M59" s="3">
+        <v>400</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E60" s="3">
         <v>77900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>64600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>181500</v>
+      </c>
+      <c r="E61" s="3">
         <v>144600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>144300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>24800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4282,19 +4425,22 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>2900</v>
-      </c>
-      <c r="X61" s="3">
-        <v>600</v>
       </c>
       <c r="Y61" s="3">
         <v>600</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4340,35 +4486,38 @@
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>400</v>
-      </c>
-      <c r="U62" s="3">
-        <v>200</v>
       </c>
       <c r="V62" s="3">
         <v>200</v>
       </c>
       <c r="W62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>252300</v>
+      </c>
+      <c r="E66" s="3">
         <v>222400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>208900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>22100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7900</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-282100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-172700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-60500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-53600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-49800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-48500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-46900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-31100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-23200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6300</v>
-      </c>
-      <c r="S72" s="3">
-        <v>-3600</v>
       </c>
       <c r="T72" s="3">
         <v>-3600</v>
       </c>
       <c r="U72" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="V72" s="3">
         <v>-3700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-51900</v>
+      </c>
+      <c r="E76" s="3">
         <v>48700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>210800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>90100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>36900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>27100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>28700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>28400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>29500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>24800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-109300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-178900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>66700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-2600</v>
       </c>
       <c r="R81" s="3">
         <v>-2600</v>
       </c>
       <c r="S81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5624,22 +5823,22 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
+        <v>200</v>
+      </c>
+      <c r="G83" s="3">
         <v>1000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -5648,46 +5847,49 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>400</v>
-      </c>
-      <c r="V83" s="3">
-        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>300</v>
       </c>
       <c r="X83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>800</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
       <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6170,70 +6391,73 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-105100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6529,8 +6763,8 @@
       <c r="Q96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
+      <c r="R96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,82 +7021,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E100" s="3">
         <v>8500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>39400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>112100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-2700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2000</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>11000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>800</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6899,8 +7148,8 @@
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>12400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2800</v>
       </c>
     </row>
